--- a/database.xlsx
+++ b/database.xlsx
@@ -397,11 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,12 +423,34 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>JIAXING ALL-LINK HOUSEWARE PRODUCTS CO., LTD.</v>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>580-81-03875</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>321-86-03228</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>